--- a/templates/template-figurine.xlsx
+++ b/templates/template-figurine.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Figurine" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Istruzioni" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Figurine" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Istruzioni" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -466,7 +466,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O1"/>
+  <dimension ref="A1:M1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -490,75 +490,65 @@
     <row r="1" ht="30" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Serie</t>
+          <t>Sottoserie</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>Sottoserie</t>
+          <t>Numero</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>Numero</t>
+          <t>Nome</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>Nome</t>
+          <t>Versione</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>Versione</t>
+          <t>Figurina di partenza</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>Figurina di partenza</t>
+          <t>Tipologia di change</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>Tipologia di change</t>
+          <t>Tipologia di errore di stampa</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>Tipologia di omaggio</t>
+          <t>Retro - Categoria</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
-          <t>Tipologia di errore di stampa</t>
+          <t>Retro - Sottocategoria</t>
         </is>
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t>Retro - Categoria</t>
+          <t>Retro - Nome</t>
         </is>
       </c>
       <c r="K1" s="1" t="inlineStr">
         <is>
-          <t>Retro - Sottocategoria</t>
+          <t>Retro - Tipo di change</t>
         </is>
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
-          <t>Retro - Nome</t>
+          <t>Retro - Tipo di omaggio</t>
         </is>
       </c>
       <c r="M1" s="1" t="inlineStr">
-        <is>
-          <t>Retro - Tipo di change</t>
-        </is>
-      </c>
-      <c r="N1" s="1" t="inlineStr">
-        <is>
-          <t>Retro - Tipo di omaggio</t>
-        </is>
-      </c>
-      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>Retro - Tipo di errore</t>
         </is>
@@ -575,7 +565,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B38"/>
+  <dimension ref="A1:B36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -592,7 +582,7 @@
     <row r="2">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>Formato delle colonne: v6.351, meno la Taglia (tolta nella v6.363).</t>
+          <t>Formato delle colonne: v6.351, meno la Taglia (v6.363), la Serie e la Tipologia di omaggio (v6.973).</t>
         </is>
       </c>
     </row>
@@ -637,7 +627,7 @@
     <row r="9">
       <c r="A9" s="3" t="inlineStr">
         <is>
-          <t>3. Le righe con Serie diversa da quella selezionata vengono ignorate, non sono un errore.</t>
+          <t>3. Tutte le righe vanno nella serie scelta nella finestra: la colonna Serie non c'e' piu'.</t>
         </is>
       </c>
     </row>
@@ -713,6 +703,7 @@
         </is>
       </c>
     </row>
+    <row r="22"/>
     <row r="23">
       <c r="A23" s="6" t="inlineStr">
         <is>
@@ -728,178 +719,154 @@
     <row r="24">
       <c r="A24" s="4" t="inlineStr">
         <is>
-          <t>Serie</t>
+          <t>Numero</t>
         </is>
       </c>
       <c r="B24" s="7" t="inlineStr">
         <is>
-          <t>Nome completo della serie. Obbligatoria.</t>
+          <t>Numero della figurina. Vuoto per le serie senza numero, e per omaggi ed errori di stampa (lo ereditano dalla partenza).</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="4" t="inlineStr">
         <is>
-          <t>Numero</t>
+          <t>Nome</t>
         </is>
       </c>
       <c r="B25" s="7" t="inlineStr">
         <is>
-          <t>Numero della figurina. Vuoto per le serie senza numero, e per omaggi ed errori di stampa (lo ereditano dalla partenza).</t>
+          <t>Nome della figurina.</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="4" t="inlineStr">
         <is>
-          <t>Nome</t>
+          <t>Sottoserie</t>
         </is>
       </c>
       <c r="B26" s="7" t="inlineStr">
         <is>
-          <t>Nome della figurina.</t>
+          <t>Solo se la serie ha sottoserie.</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="4" t="inlineStr">
         <is>
-          <t>Sottoserie</t>
+          <t>Versione</t>
         </is>
       </c>
       <c r="B27" s="7" t="inlineStr">
         <is>
-          <t>Solo se la serie ha sottoserie.</t>
+          <t>Uno dei sei valori qui sopra. Obbligatoria.</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="4" t="inlineStr">
         <is>
-          <t>Versione</t>
+          <t>Figurina di partenza</t>
         </is>
       </c>
       <c r="B28" s="7" t="inlineStr">
         <is>
-          <t>Uno dei sei valori qui sopra. Obbligatoria.</t>
+          <t>SOLO per le versioni non base. Numero della figurina di partenza, o Nome se non ha numero.</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="4" t="inlineStr">
         <is>
-          <t>Figurina di partenza</t>
+          <t>Tipologia di change</t>
         </is>
       </c>
       <c r="B29" s="7" t="inlineStr">
         <is>
-          <t>SOLO per le versioni non base. Numero della figurina di partenza, o Nome se non ha numero.</t>
+          <t>Solo con Versione = change. Una delle tipologie configurate sulla serie. Per un change di RETRO si lascia vuota: il tipo lo prende dal retro indicato.</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="4" t="inlineStr">
         <is>
-          <t>Tipologia di change</t>
+          <t>Tipologia di errore di stampa</t>
         </is>
       </c>
       <c r="B30" s="7" t="inlineStr">
         <is>
-          <t>Solo con Versione = change. Deve essere una delle tipologie configurate sulla serie.</t>
+          <t>Solo con Versione = errore di stampa. Idem. Per un errore sul RETRO si lascia vuota: il tipo lo prende dal retro indicato.</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="4" t="inlineStr">
         <is>
-          <t>Tipologia di omaggio</t>
+          <t>Retro - Categoria</t>
         </is>
       </c>
       <c r="B31" s="7" t="inlineStr">
         <is>
-          <t>Solo con Versione = omaggio. Idem.</t>
+          <t>Categoria del retro da agganciare.</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="4" t="inlineStr">
         <is>
-          <t>Tipologia di errore di stampa</t>
+          <t>Retro - Sottocategoria</t>
         </is>
       </c>
       <c r="B32" s="7" t="inlineStr">
         <is>
-          <t>Solo con Versione = errore di stampa. Idem.</t>
+          <t>Facoltativa. Serve quando due retro hanno lo stesso Nome in sottocategorie diverse: senza, la riga viene scartata elencando fra quali scegliere.</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="4" t="inlineStr">
         <is>
-          <t>Retro - Categoria</t>
+          <t>Retro - Nome</t>
         </is>
       </c>
       <c r="B33" s="7" t="inlineStr">
         <is>
-          <t>Categoria del retro da agganciare.</t>
+          <t>Nome del retro da agganciare.</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="4" t="inlineStr">
         <is>
-          <t>Retro - Sottocategoria</t>
+          <t>Retro - Tipo di change</t>
         </is>
       </c>
       <c r="B34" s="7" t="inlineStr">
         <is>
-          <t>Facoltativa. Serve quando due retro hanno lo stesso Nome in sottocategorie diverse: senza, la riga viene scartata elencando fra quali scegliere.</t>
+          <t>Compila solo se il retro da agganciare e' a sua volta un change.</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="4" t="inlineStr">
         <is>
-          <t>Retro - Nome</t>
+          <t>Retro - Tipo di omaggio</t>
         </is>
       </c>
       <c r="B35" s="7" t="inlineStr">
         <is>
-          <t>Nome del retro da agganciare.</t>
+          <t>Obbligatoria per una figurina omaggio: un omaggio lo e' sempre grazie al retro, e il tipo e' quello del retro. Non c'e' piu' la colonna «Tipologia di omaggio».</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="4" t="inlineStr">
         <is>
-          <t>Retro - Tipo di change</t>
+          <t>Retro - Tipo di errore</t>
         </is>
       </c>
       <c r="B36" s="7" t="inlineStr">
-        <is>
-          <t>Compila solo se il retro da agganciare e' a sua volta un change.</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" s="4" t="inlineStr">
-        <is>
-          <t>Retro - Tipo di omaggio</t>
-        </is>
-      </c>
-      <c r="B37" s="7" t="inlineStr">
-        <is>
-          <t>Solo se il retro da agganciare e' un omaggio.</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" s="4" t="inlineStr">
-        <is>
-          <t>Retro - Tipo di errore</t>
-        </is>
-      </c>
-      <c r="B38" s="7" t="inlineStr">
         <is>
           <t>Solo se il retro da agganciare e' un errore di stampa.</t>
         </is>
